--- a/GOZ_2910.xlsx
+++ b/GOZ_2910.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$H$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,7 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -657,80 +657,80 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>0887100000226000028</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>ФГКУ «УВО ВНГ России по ХМАО – Югре», Ханты-Мансийск (ИНН 8601047640)</t>
+          <t>ФКУЗ «МСЧ МВД России по г. Санкт-Петербургу и Ленинградской области» (ИНН 784232</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудования электрического осветительного: панели светодиодные накладные 120 шт,</t>
+          <t xml:space="preserve">Поставка реагентов ИВД для биохимии/иммунотурбидиметрии (38 позиций: наборы, калибраторы, </t>
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>450700</v>
+        <v>3928514.73</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>2026-11-10 10:00 (GMT+5) = 08:00 МСК</t>
+          <t>2026-11-13 09:00 МСК</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>350250</v>
+        <v>2687290</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.2229</v>
+        <v>0.316</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>47073</v>
+        <v>721117</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>8764</v>
+        <v>387194</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.2229</v>
+        <v>0.316</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>4 507 ₽ (1%) / 22 535 ₽ (5%), л/с 05871D11920</t>
+          <t>39 285,15 ₽ (1%) — на спецсчёт/ЭТП или независимая гарантия / 785 702,95 ₽ (20%!) — БГ (ст.45, срок &gt; срока исполнения на 1 мес.) или деньги на л/с УФК; при снижении ≥25% — антидемпинг ст.37 (×1,5)</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>г. Ханты-Мансийск, ул. Мира, д. 13; срок — в контракте (план-график: исполнение в 2026 г., 30 дней до начала исполнения с даты заключения)</t>
+          <t>СПб, ул. Малая Морская, 10 лит. А; исполнение 01.01.2027–31.12.2027 — по годовому сроку очевидно поставка партиями по заявкам (график в проекте контракта, не приложен); реагенты — холодовая цепь 2–8 °C, остаточный срок годности по ТЗ</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет 2026, КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки (условия в проекте контракта, не приложен)</t>
+          <t>Федеральный бюджет 2027 (вся сумма на первый плановый год), КВР 244, БО от 27.10.2026; конкретный срок — в проекте контракта (не приложен); по 44-ФЗ н</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПП 1875, Прил. 2 — ОГРАНИЧЕНИЕ по ОКПД2 27.40.25.123: в заявке номер реестровой записи из реестра российской РЭП или Евразийского реестра; при наличии хотя бы одной заявки с российским товаром заявки </t>
+          <t>ПП РФ №1875: «Ограничение» — 26 позиций (АЛТ, АСТ, альбумин, ЩФ, билирубины, Ca, креатинин, ГГТ, ЛДГ, глюкоза, ЛПВП, ЛПНП, железо, липаза, микроальбумин, холестерин, белок, ТГ, мочевина, мочевая к-та,</t>
         </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>ET44; TOVNPIVR; страна происхождения + номер реестровой записи РЭП/ЕАЭС в заявке; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+          <t>ET44 (ч.1 ст.31), TOVNPIVR (нет в РНП за отказ из-за санкций); аккредитация на АСТ ГОЗ (закрытая процедура, ТЗ и проект контракта выдаются только участникам); РУ Росздравнадзора на каждый набор; лицензии не требуются (ИВД — не фарма); фактически — поставщик должен уметь подтвердить совместимость с а</t>
         </is>
       </c>
       <c r="R3" s="9" t="inlineStr">
         <is>
-          <t>Условно (низкий приоритет): выгодно только с нереестровым товаром (ЭРА и аналоги, ~22% маржи) — но при любой заявке с ре</t>
+          <t>Не идти вслепую. Идти только если после получения ТЗ на АСТ ГОЗ (до 13.11) анализатор окажется открытым/с российскими ад</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>Ограничение ПП 1875: без номера в реестре РЭП/ЕАЭС заявка отклоняется при наличии хотя бы одной российской заявки; НМЦ сформирована по ценам китайских панелей; реестровые аналоги в 3–4 раза дороже; Характеристики (мощность, световой поток, IP, Ra, пульсация, гарантия) — только в ТЗ; несоответствие ЭРА требованиям ТЗ; Преимущество 15% организациям инвалидов; Поставка до конца 2026 в ХМАО, бой при п</t>
+          <t>Анализатор заказчика в карточке НЕ указан — главный риск несовместимости и отказа в приёмке; себестоимость по всем 38 строкам — оценка (±30%), КП не получены; Нацрежим: 26 позиций с ограничением ПП 1875 — нужны российские наборы с реестровой записью; если под анализатор их нет, заявку с иностранным товаром отклонят при наличии хотя бы одной «российской» заявки; Обеспечение контракта 20% (785,7 тыс</t>
         </is>
       </c>
     </row>
@@ -740,80 +740,80 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0338100006526000023</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
+          <t>Филиал №2 ФГКУ «1477 Военно-морской клинический госпиталь» Минобороны России (Пе</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
+          <t>Поставка бахил водонепроницаемых, 204 000 шт (ОКПД2 32.50.50.190)</t>
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>283105.45</v>
+        <v>842520</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00</t>
+          <t>2026-11-13 09:00 (GMT+12) = 00:00 МСК 13.11.2026 (фактически ночь 12→13.11 по Москве!)</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>221000</v>
+        <v>393780</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.5326</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>28726</v>
+        <v>309815</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>4662</v>
+        <v>238201</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.5326</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>нет / нет</t>
+          <t>не установлено (НМЦК &lt; 1 млн) / 42 126 ₽ (5%) — порядок в документации</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
+          <t>г. Петропавловск-Камчатский, ул. Аммональная Падь, 1; срок 11.01.2027–31.12.2027 — вероятно партиями по заявкам в течение года (график в проекте контракта, не приложен)</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
+          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
+          <t>ПП 1875 «Преимущество» (15%): российские бахилы — нужна реестровая запись/страна происхождения; иностранный товар — контракт по цене минус 15%. Плюс преимущество организациям инвалидов 15% (ст.29)</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
+          <t>ET44 (ч.1 ст.31), TOVNPIVR; аккредитация на АСТ ГОЗ; РУ на медизделие; характеристики (плотность, толщина, длина, двойная резинка) в карточке не указаны — в ТЗ. КТРУ 32.50.50.190-00001158 «Бахилы водонепроницаемые» — исключена; средняя цена по ней 4,0 ₽ (https://analitikamed.ru/ktru_detail/46265/)</t>
         </is>
       </c>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
+          <t>Идти (приоритет №1 из трёх), если ТЗ требует обычные ПНД/ПВД бахилы 3–4 г/пара: маржа при НМЦК ~53%, запас до безубыточн</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
+          <t xml:space="preserve">Характеристики не известны: если «водонепроницаемые» = высокие двухслойные ≥60 мкм (как в части ТЗ по этой КТРУ) — себестоимость 4–8 ₽/шт, маржи нет; Высокая маржа = много участников (вкл. организации инвалидов с преимуществом 15%) — вероятно снижение 30–50%; при ≥25% — антидемпинг: обеспечение ×1,5; Доставка на Камчатку по заявкам в течение 2027 г. — каждая партия сборным грузом 30–45 дней, риск </t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0887100000226000028</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -833,70 +833,70 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
+          <t>ФГКУ «УВО ВНГ России по ХМАО – Югре», Ханты-Мансийск (ИНН 8601047640)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
+          <t>Поставка оборудования электрического осветительного: панели светодиодные накладные 120 шт,</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>58890</v>
+        <v>450700</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
+          <t>2026-11-10 10:00 (GMT+5) = 08:00 МСК</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>57140</v>
+        <v>350250</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.2229</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>-4139</v>
+        <v>47073</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-10028</v>
+        <v>8764</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.2229</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
+          <t>4 507 ₽ (1%) / 22 535 ₽ (5%), л/с 05871D11920</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
+          <t>г. Ханты-Мансийск, ул. Мира, д. 13; срок — в контракте (план-график: исполнение в 2026 г., 30 дней до начала исполнения с даты заключения)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
+          <t>Федеральный бюджет 2026, КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки (условия в проекте контракта, не приложен)</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
+          <t xml:space="preserve">ПП 1875, Прил. 2 — ОГРАНИЧЕНИЕ по ОКПД2 27.40.25.123: в заявке номер реестровой записи из реестра российской РЭП или Евразийского реестра; при наличии хотя бы одной заявки с российским товаром заявки </t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
+          <t>ET44; TOVNPIVR; страна происхождения + номер реестровой записи РЭП/ЕАЭС в заявке; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
+          <t>Условно (низкий приоритет): выгодно только с нереестровым товаром (ЭРА и аналоги, ~22% маржи) — но при любой заявке с ре</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
+          <t>Ограничение ПП 1875: без номера в реестре РЭП/ЕАЭС заявка отклоняется при наличии хотя бы одной российской заявки; НМЦ сформирована по ценам китайских панелей; реестровые аналоги в 3–4 раза дороже; Характеристики (мощность, световой поток, IP, Ra, пульсация, гарантия) — только в ТЗ; несоответствие ЭРА требованиям ТЗ; Преимущество 15% организациям инвалидов; Поставка до конца 2026 в ХМАО, бой при п</t>
         </is>
       </c>
     </row>
@@ -906,70 +906,80 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>0348100063126000025</t>
+          <t>260000141501024</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>УМВД России по г.о. Химки (ИНН 5047015587)</t>
+          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Оказание услуг по подготовке зданий и сооружений к отопительному сезону: подготовка систем</t>
+          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>312000</v>
+        <v>283105.45</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>2026-11-09 11:00 МСК</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="8" t="n"/>
+          <t>2026-11-02 12:00</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>221000</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>28726</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>4662</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0.2194</v>
+      </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>не установлено (в карточке нет; НМЦК &lt; 1 млн) / 31 200 ₽ (10%), БГ или деньги</t>
+          <t>нет / нет</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Химки: ул. Гоголя, 4 (подвал, ИТП), ул. Гоголя, 6 (зд. «а» и «б»: подвал, 1 этаж ДЧ, архив, кабинеты, чердак), ул. Лавочкина, 12А, пр-т Мира, 23 «а», Вашутинское ш., 22Д; срок исполнения — до 31.12.2026</t>
+          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет 2026, КВР 244; порядок оплаты в проекте контракта (не приложен); по 44-ФЗ — не более 7 раб. дней с даты подписания документа о приё</t>
+          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Не указан (услуга)</t>
+          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31 44-ФЗ); TOVNPIVR (нет в РНП за отказ из-за санкций против заказчика); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
-        </is>
-      </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>Не идти — не наш профиль (услуги, нужна своя сантехническая бригада или субподрядчик); отопительный сезон уже идёт, срок</t>
+          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Исполнение только через субподрядчика — маржа посредника на работах мала, ответственность за качество и сроки на нас; Приёмка работ по актам на режимном объекте МВД, допуск персонала; Обеспечение 31,2 тыс. ₽ и штрафы 44-ФЗ при узком сроке (до 31.12.2026)</t>
+          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
         </is>
       </c>
     </row>
@@ -979,70 +989,80 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0172400000226000017</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24); цена единицы — сумма цен единиц (ч.24 ст.22 44-ФЗ)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ГУ Росгвардии по г. Санкт-Петербургу и Ленинградской области (ИНН 7842119240)</t>
+          <t>Управление ФСБ России по Республике Тыва (ИНН 1701032940)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Поставка запасных частей для ремонта военной и специальной техники в 2027 году (ОКПД2 29.3</t>
+          <t>Поставка изделий медицинского назначения (8 позиций: пластырь, скарификаторы, перчатки нит</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2000000</v>
+        <v>208172.52</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-11-13 09:00 МСК</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="8" t="n"/>
+          <t>2026-11-17 05:00 (GMT+4) = 04:00 МСК</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>162824</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0.2178</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>20852</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>3157</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0.2178</v>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>20 000 ₽ (1%) / 200 000 ₽ (10%) + обеспечение гарантийных обязательств 200 000 ₽ (10%)</t>
+          <t>не установлено (НМЦК &lt; 1 млн) / 20 817,25 ₽ (10%) — БГ (ст.45, п.13 документации) или деньги</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>По адресу, указанному в заявке заказчика, в пределах Санкт-Петербурга, раб. дни 9:00–16:00 (обед 13–14); исполнение 01.01.2027–31.12.2027</t>
+          <t>г. Кызыл, ул. Дружбы, 42А; срок исполнения 01.01.2027–01.05.2027 (разово или партиями — в проекте контракта, не приложен)</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Федеральный бюджет 2027 (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки каждой партии; гарантия — не менее заводской, а </t>
+          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>В карточке по позиции не указан (графа пустая) — проверить в извещении/ТЗ</t>
+          <t>В карточке по всем 8 позициям графа нацрежима ПУСТАЯ (при этом перчатки/шприцы/иглы обычно входят в перечни ПП 1875) — проверить в документации; если ограничение есть — нужен российский товар с реестр</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>ET44; TOVNPIVR; участник не под спецмерами Указа №252 и не под контролем таких лиц; ответственность за антиконкурентные соглашения; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+          <t>ET44 (ч.1 ст.31); аккредитация на АСТ ГОЗ; РУ на медизделия; ТЗ/характеристики (объёмы шприцев, размеры бинта, фасовка) в карточке не указаны</t>
         </is>
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Не подавать вслепую — запросить ТЗ/обоснование НМЦК; решение после сверки цен единиц. Потенциально интересно (2 млн ₽ в </t>
+          <t>Низкий приоритет / скорее не идти: прибыль ~21 тыс.₽ при −10% и ~3 тыс.₽ при −20%, безубыточность ~−22%. Подавать только</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безубыточное снижение = средняя наценка цен единиц ТЗ над рынком; торг по сумме цен единиц часто уходит на 30–60%; Заказчик не обязан выбрать весь лимит 2 млн ₽ — выручка не гарантирована; Спецтехника (БТР, «Тайфун», «Тигр», Урал) — часть позиций только у заводов/дилеров, длинные сроки, возможен запрет аналогов; Сроки поставки по заявке (часы/дни) и штрафы — в проекте контракта; Заморозка 200+200 </t>
+          <t>Единицы измерения позиций 1, 2, 8 (пластырь «шт» 1 817 ₽, скарификатор «шт» 800 ₽, вата «уп» 296 ₽) без ТЗ непонятны — себестоимость по ним оценка; Нацрежим в карточке не заполнен — возможно, ограничение указано в документации (перчатки, шприцы); Маленький контракт — логистика до Кызыла и БГ съедают заметную долю; при раздельных партиях прибыль падает; Кызыл: только автодоставка, сроки ТК 10–20 дн</t>
         </is>
       </c>
     </row>
@@ -1052,66 +1072,295 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>58890</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>57140</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>-4139</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>-10028</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>0348100063126000025</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>УМВД России по г.о. Химки (ИНН 5047015587)</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Оказание услуг по подготовке зданий и сооружений к отопительному сезону: подготовка систем</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-09 11:00 МСК</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>не установлено (в карточке нет; НМЦК &lt; 1 млн) / 31 200 ₽ (10%), БГ или деньги</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>Химки: ул. Гоголя, 4 (подвал, ИТП), ул. Гоголя, 6 (зд. «а» и «б»: подвал, 1 этаж ДЧ, архив, кабинеты, чердак), ул. Лавочкина, 12А, пр-т Мира, 23 «а», Вашутинское ш., 22Д; срок исполнения — до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Федеральный бюджет 2026, КВР 244; порядок оплаты в проекте контракта (не приложен); по 44-ФЗ — не более 7 раб. дней с даты подписания документа о приё</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Не указан (услуга)</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>ET44 (ч.1 ст.31 44-ФЗ); TOVNPIVR (нет в РНП за отказ из-за санкций против заказчика); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>Не идти — не наш профиль (услуги, нужна своя сантехническая бригада или субподрядчик); отопительный сезон уже идёт, срок</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Исполнение только через субподрядчика — маржа посредника на работах мала, ответственность за качество и сроки на нас; Приёмка работ по актам на режимном объекте МВД, допуск персонала; Обеспечение 31,2 тыс. ₽ и штрафы 44-ФЗ при узком сроке (до 31.12.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>0172400000226000017</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24); цена единицы — сумма цен единиц (ч.24 ст.22 44-ФЗ)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ГУ Росгвардии по г. Санкт-Петербургу и Ленинградской области (ИНН 7842119240)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Поставка запасных частей для ремонта военной и специальной техники в 2027 году (ОКПД2 29.3</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-13 09:00 МСК</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>20 000 ₽ (1%) / 200 000 ₽ (10%) + обеспечение гарантийных обязательств 200 000 ₽ (10%)</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>По адресу, указанному в заявке заказчика, в пределах Санкт-Петербурга, раб. дни 9:00–16:00 (обед 13–14); исполнение 01.01.2027–31.12.2027</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Федеральный бюджет 2027 (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки каждой партии; гарантия — не менее заводской, а </t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>В карточке по позиции не указан (графа пустая) — проверить в извещении/ТЗ</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>ET44; TOVNPIVR; участник не под спецмерами Указа №252 и не под контролем таких лиц; ответственность за антиконкурентные соглашения; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Не подавать вслепую — запросить ТЗ/обоснование НМЦК; решение после сверки цен единиц. Потенциально интересно (2 млн ₽ в </t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Безубыточное снижение = средняя наценка цен единиц ТЗ над рынком; торг по сумме цен единиц часто уходит на 30–60%; Заказчик не обязан выбрать весь лимит 2 млн ₽ — выручка не гарантирована; Спецтехника (БТР, «Тайфун», «Тигр», Урал) — часть позиций только у заводов/дилеров, длинные сроки, возможен запрет аналогов; Сроки поставки по заявке (часы/дни) и штрафы — в проекте контракта; Заморозка 200+200 </t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>260003123900911</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, по итогам — договор)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>АО «ЦС «Звёздочка», филиал «35 СРЗ», Мурманск, ул. Адмирала флота Лобова, 100 (И</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Вооружение рукава 511-77.012 — 6 шт (ОКПД2 22.19.30.139), ГОЗ</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>2026-11-03 08:00</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>нет / нет</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>До терминала транспортной компании в г. Мурманске в течение 30 к.д. с даты получения 100% оплаты (в тексте «силами и за счёт средств Покупателя» — уточнить, кто оплачивает перевозку до Мурманска)</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>100% предоплата в течение 30 к.д. с момента получения счёта, с отдельного счёта Покупателя в ПАО «Банк ПСБ», ИГК 1619187304551432209007007 → у нас нуж</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>В карточке лота — запрет закупок иностранных товаров; в Заявке.docx — запреты/ограничения/преимущество ПП 1875 НЕ применяются (абз.3 пп.«и» п.4) — противоречие, уточнить. Аналог не допускается; указан</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Счёт/КП в составе заявки; товар 2026 г. выпуска, новый, заводская упаковка; паспорта/сертификаты; документация на русском по ГОСТ Р 2.601-2019, 2.610-2019 с учётом ГОСТ РВ 0002-601-2019; РКД на изготовление поставщик приобретает за свой счёт у КБ-держателя; ГОЗ: отдельный счёт, раздельный учёт</t>
         </is>
       </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="R11" s="9" t="inlineStr">
         <is>
           <t>Не идти без расшифровки — срочно (до 03.11) запросить у заказчика параметры изделия; идти только при найденном изготовит</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Позиция не расшифрована: что запросить — чертёж/параметры 511-77.012 (тип рукава, DN, PN, длина, среда, тип и материал арматуры, ГОСТ/ОСТ), держатель КД (КБ), прежние поставщики и цены, вид приёмки (ОТК/ВП МО), требования к консервации и упаковке, кто платит доставку до Мурманска; Покупка РКД у КБ за наш счёт — для посредника почти нереально в 5 дней; ГОЗ: отдельный счёт в уполномоченном банке, ра</t>
         </is>
@@ -1129,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1187,284 +1436,284 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>0887100000226000028</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Панель светодиодная универсальная (накладная), 36 Вт 595×595 (характеристики в ТЗ)</t>
+          <t>1. Аланинаминотрансфераза (АЛТ) ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E2" s="14" t="n">
-        <v>1050</v>
+        <v>6984.51</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>850</v>
+        <v>3492.26</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.499999284130168</v>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>оценка по нереестровому аналогу ЭРА SPO-6-36 (накладной/встраиваемый монтаж) 707–790 ₽ + запас на накладной корпус: https://www.vseinstrumenti.ru/product/svetodiodnyj-svetilnik-era-spo-6-36-6k-p-595x595x19-36vt-3060lm-6500k-ip40-prizma-b0039056-11171</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>0887100000226000028</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Панель светодиодная универсальная (встраиваемая для потолков Армстронг) 595×595</t>
+          <t>2. Альбумин ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1140</v>
+        <v>3369.62</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>775</v>
+        <v>1684.81</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>0.3201754385964912</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>ЭРА SPO-6-36-6K-P 773,72 ₽ при &gt;50 шт (LEDPremium), 707 ₽ ВсеИнструменты, РРЦ 789,65 ₽: https://ledpremium.ru/catalog/ofisnye_svetodiodnye_svetilniki/spo_6_36_6k_p_era_svetodiod_sv_k_595x595x19_36vt_3060lm_6500k_prizma_4_96/ ; реестровые: https://ter</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>0887100000226000028</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Светильник светодиодный (тип/мощность в карточке не указаны)</t>
+          <t>3. Общая щелочная фосфатаза (ЩФ) ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1250</v>
+        <v>5558.13</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>900</v>
+        <v>2779.07</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.28</v>
+        <v>0.4999991004168668</v>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>оценка: характеристики только в ТЗ; принят уровень массового нереестрового светильника ~900 ₽</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
+          <t xml:space="preserve">4. Бета-гемолитический стрептококк А антитела к стрептолизину O ИВД, набор, нефелометрический/турбидиметрический анализ </t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>550</v>
+        <v>2</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E5" s="14" t="n">
-        <v>514.74</v>
+        <v>34354.11</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>380</v>
+        <v>27483.29</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.2617632202665423</v>
+        <v>0.1999999417828027</v>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
+          <t>5. Аспартатаминотрансфераза ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>7244.52</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>3622.26</v>
+      </c>
+      <c r="G6" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>14400</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>11580</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.1958333333333333</v>
-      </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
+          <t>6. Конъюгированный (прямой, связанный) билирубин ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E7" s="14" t="n">
-        <v>792</v>
+        <v>3657</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>900</v>
+        <v>1828.5</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.1363636363636365</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Песок (строительный, по ТЗ)</t>
+          <t>7. Общий билирубин ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E8" s="14" t="n">
-        <v>654</v>
+        <v>3657</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>990</v>
+        <v>1828.5</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.5137614678899083</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
+          <t>8. C-реактивный белок (СРБ) ИВД, набор, нефелометрический/турбидиметрический анализ [Преимущество]</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>п.м</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E9" s="14" t="n">
-        <v>300</v>
+        <v>14365.88</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>200</v>
+        <v>11492.7</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.2000002784375199</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>0348100063126000025</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Работы/услуги по подготовке системы отопления к сезону и ППР (промывка/опрессовка, обслуживание ИТП и т.п. — состав в ТЗ</t>
+          <t>9. Кальций (Ca2+) ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1472,80 +1721,1678 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>усл. ед.</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="E10" s="14" t="n">
-        <v>312000</v>
-      </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+        <v>2630.64</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1315.32</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Себестоимость не оценивалась: это работы (персонал-сантехники, оборудование для промывки/опрессовки, допуск на объекты МВД), не поставка товара</t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>0172400000226000017</t>
+          <t>0372100021526000159</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Запчасти для ремонта ВиСТ — перечень в ТЗ (в карточке одна обобщённая позиция)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>по заявкам до исчерпания 2 000 000 ₽</t>
-        </is>
+          <t>10. Креатинин ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>10365.71</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>5182.85</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.500000482359626</v>
+      </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">«Цена за единицу» 6 458 937 848,97 ₽ — это не цена товара, а СУММА начальных цен единиц всех позиций каталога (ч.24 ст.22 44-ФЗ: количество заранее не определено). Торг идёт по снижению этой суммы; контракт заключается на максимальное значение 2 000 </t>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>11. Ферритин ИВД, набор, иммунотурбидиметрический анализ [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>26484.3</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>21187.44</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>12. Гамма-глутамилтрансфераза (ГГТ) ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>12146.84</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>6073.42</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>13. Общая лактатдегидрогеназа ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>6551.86</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>3275.93</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>14. Глюкоза ИВД, набор,  ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>5108.64</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2554.32</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>15. Общий гемоглобин ИВД, набор, ферментный спектрофотометрический анализ [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>184365.85</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>147492.68</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>16. Холестерин липопротеинов высокой плотности ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>57727.75</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>28863.88</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.4999999133865428</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>17. Железо ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>10085.7</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>5042.85</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>18. Холестерин липопротеинов низкой плотности ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>64912.27</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>32456.13</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.5000000770270396</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>19. Липаза ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>35569.96</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>17784.98</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>20. Микроальбумин ИВД, набор, иммунотурбидиметрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>38138.49</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>19069.24</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0.5000001311011526</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>21. Ревматоидный фактор ИВД, набор, иммунотурбидиметрический анализ [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>22003.05</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>17602.44</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>22. Общий холестерин ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>7512.96</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>3756.48</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>23. Общий белок ИВД, набор, спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>3994.91</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1997.45</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0.5000012515926516</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>24. Триглицериды ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>15389.09</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>7694.55</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.4999996750944987</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>25. Ненасыщенная железосвязывающая способность ИВД, набор, спектрофотометрический анализ [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>20437.72</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>16350.18</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0.1999998042834524</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>26. Мочевина/азот мочевины ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>6588.71</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>3294.36</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0.4999992411261082</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>27. Мочевая кислота ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>8779.33</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>4389.66</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0.500000569519542</v>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>28. Общая амилаза ИВД, набор, ферментный спектрофотометрический анализ [Ограничение]</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>23365.22</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>11682.61</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>оценка 50% НМЦ: российские аналоги (Вектор-Бест «…-Ново», Диакон-ДС «ДиаС», ДДС, Ольвекс) — в каталоге дистрибьютора https://animed74.ru/product/naboryi-vektor-best (цены без даты) наборы ~0,4–3,5 тыс.₽ (напр. АЛТ-УФ-Ново 1 762 ₽, ЛВП-Холестерин-Ново</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>29. Ферритин ИВД, калибратор [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>50849.56</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>40679.65</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0.1999999606682928</v>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>30. Множественные липидные аналиты ИВД, калибратор [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>18195.52</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>14556.42</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0.1999997801656672</v>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>31. Множественные аналиты клинической химии ИВД, калибратор [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>21197.76</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>16958.21</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0.1999999056504084</v>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>32. Множественные белки клинической химии ИВД, калибратор [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>24784.23</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>19827.38</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0.2000001613929502</v>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>33. Множественные аналиты клинической химии ИВД, контрольный материал [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>14661.69</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>11729.35</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0.2000001364099228</v>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>34. Микроальбумин ИВД, калибратор [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>12966.88</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>10373.5</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>0.2000003084782153</v>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>35. Микроальбумин ИВД, контрольный материал [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>3163.29</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>2530.63</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>0.2000006322531288</v>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>36. Множественные аналиты клинической химии ИВД, контрольный материал [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>27033.8</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>21627.04</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>37. Множественные аналиты клинической химии ИВД, контрольный материал [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>31266.61</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>25013.29</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>0.1999999360339992</v>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>0372100021526000159</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>38. Моющий/чистящий раствор ИВД, для автоматических/полуавтоматических систем [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>52357</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>41885.6</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>оценка 80% НМЦ: позиция «Преимущество» (иммунотурбидиметрия/калибраторы/контроли/моющий р-р) — как правило, оригинал производителя закрытого анализатора; закупка у официального дистрибьютора с маржой 15–25%; российский аналог даёт право на преимущест</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>0338100006526000023</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Бахилы водонепроницаемые [Преимущество]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>204000</v>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>0.6198547215496368</v>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>ОФСИ: бахилы ПЭ повышенной плотности 35 мкм, 3,5 г, 50 пар — 174 ₽/уп (1,74 ₽/шт) https://www.ofsi.ru/product/bakhily_n_s_p_e_prochnye_gladkie_3_5g_art40_oranzhevye_50par_up.html → −10% = 1,57 ₽/шт; Элегрин Экстра плюс 3,5 г опт 113–129 ₽/50 пар (1,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>0887100000226000028</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Панель светодиодная универсальная (накладная), 36 Вт 595×595 (характеристики в ТЗ)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>850</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>оценка по нереестровому аналогу ЭРА SPO-6-36 (накладной/встраиваемый монтаж) 707–790 ₽ + запас на накладной корпус: https://www.vseinstrumenti.ru/product/svetodiodnyj-svetilnik-era-spo-6-36-6k-p-595x595x19-36vt-3060lm-6500k-ip40-prizma-b0039056-11171</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>0887100000226000028</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Панель светодиодная универсальная (встраиваемая для потолков Армстронг) 595×595</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>775</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>0.3201754385964912</v>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>ЭРА SPO-6-36-6K-P 773,72 ₽ при &gt;50 шт (LEDPremium), 707 ₽ ВсеИнструменты, РРЦ 789,65 ₽: https://ledpremium.ru/catalog/ofisnye_svetodiodnye_svetilniki/spo_6_36_6k_p_era_svetodiod_sv_k_595x595x19_36vt_3060lm_6500k_prizma_4_96/ ; реестровые: https://ter</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>0887100000226000028</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Светильник светодиодный (тип/мощность в карточке не указаны)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>оценка: характеристики только в ТЗ; принят уровень массового нереестрового светильника ~900 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>260000141501024</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>514.74</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>0.2617632202665423</v>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>1. Лейкопластырь для поверхностных ран</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>1816.67</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>0.284404982743151</v>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>оценка: «шт» за 1 816,67 ₽ — вероятно упаковка/рулон (ТЗ нет); бактерицидные/фиксирующие пластыри рос. производства (Верофарм, Мирал, Медрулон) — оценка 70% НМЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>2. Ручка-скарификатор автоматическая, одноразового использования</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>оценка: 800 ₽ за «шт» — скорее упаковка ланцетов/скарификаторов-ручек (ТЗ нет); безопасные ланцеты 100 шт в опте ~500–700 ₽ — оценка, единица измерения требует проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>3. Перчатки смотровые/процедурные нитриловые, неопудренные, нестерильные</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Пара (2 шт.)</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>0.3230174081237911</v>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Webpack: нитрил смотр. неопудр. 100 шт (50 пар) 400 ₽, опт от 69 уп. 350 ₽ → 7,0 ₽/пара https://webpack.ru/sredstva-individyalnoiy-zashitu/perchatki/perchatki-nitrilovye/ ; Trial Market ~390 ₽/100 шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>4. Шприц общего назначения</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>НВ-Лаб: шприц 5 мл 3-комп. опт 3 ₽, розн. 4 ₽ https://www.nv-lab.ru/catalog_info.php?ID=6920 ; российский (Медполимер/СФМ) — оценка 3,8 ₽; объём шприца в карточке не указан (по цене 5,5 ₽ — 2–5 мл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>5. Игла для забора крови, стандартная</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>0.7816864976720124</v>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Sunmed: игла двусторонняя 21G «ЕЛАМЕД» (РФ) 8516 — 4,22 ₽ опт, цена на 14.04.2026 https://www.sunmed.ru/product/igla-dvustoronnyaya-dlya-vakuumnoy-sistemy-zabora-krovi-elamed-8516/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>6. Бинт эластичный, нелатексный, нестерильный, одноразового использования</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>315.67</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>265</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>0.1605157284505971</v>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Комета-мед: бинт эласт. компрессионный 10 см×5 м Медитек — 295 ₽ https://kometa-med.com/product/bint-elastichnyj-kompressionnyj-meditek-sr-10-sm-h-5-m/ −10% торг ≈ 265 ₽; размер в карточке не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>7. Шприц общего назначения</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>0.4246353322528363</v>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>оптовый прайс: шприц 3-комп. 20 мл — 7,90 ₽ (поиск по шприцевым оптовикам), другой магазин 5,10 ₽/шт (уп.100) → 7,1 ₽ после торга; объём в карточке не указан (10–20 мл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>8. Ватные шарики</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Упаковка</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>0.3925895930350273</v>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>оценка: «упаковка» без фасовки (ТЗ нет); шарики ватные нестерильные 100–200 шт/уп рос. пр-ва (Емельянъ Савостинъ, Амелия) — оценка 60% НМЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>11580</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>0.1958333333333333</v>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>792</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>-0.1363636363636365</v>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Песок (строительный, по ТЗ)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>654</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>990</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>-0.5137614678899083</v>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>п.м</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>0348100063126000025</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Работы/услуги по подготовке системы отопления к сезону и ППР (промывка/опрессовка, обслуживание ИТП и т.п. — состав в ТЗ</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>312000</v>
+      </c>
+      <c r="F57" s="14" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Себестоимость не оценивалась: это работы (персонал-сантехники, оборудование для промывки/опрессовки, допуск на объекты МВД), не поставка товара</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>0172400000226000017</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Запчасти для ремонта ВиСТ — перечень в ТЗ (в карточке одна обобщённая позиция)</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>по заявкам до исчерпания 2 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n"/>
+      <c r="F58" s="14" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">«Цена за единицу» 6 458 937 848,97 ₽ — это не цена товара, а СУММА начальных цен единиц всех позиций каталога (ч.24 ст.22 44-ФЗ: количество заранее не определено). Торг идёт по снижению этой суммы; контракт заключается на максимальное значение 2 000 </t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
           <t>260003123900911</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Вооружение рукава (рукав с концевой арматурой) по обозначению 511-77.012</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C59" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="14" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="13" t="inlineStr">
         <is>
           <t>НМЦ не указана (0,00) — цену формирует наше КП. Себестоимость определить нельзя: изделие изготавливается по чертежу 511-77.012 (судостроительная КД), рыночной цены нет. Метод: запрос КП у изготовителей рукавов по КД (РВД/металлорукава для флота) посл</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/GOZ_2910.xlsx
+++ b/GOZ_2910.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -906,80 +906,80 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
+          <t>закрытый аукцион 44-ФЗ</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
+          <t>Пограничное управление ФСБ России по Приморскому краю</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
+          <t>Шины пневматические (ГОЗ, ГПВ): 13 позиций — легковые 99 шт, для автобусов 28 шт, грузовые</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>283105.45</v>
+        <v>2681032.86</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00</t>
+          <t>16.11.2026 02:45 (GMT+4) = 01:45 МСК</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>221000</v>
+        <v>2367100</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.1171</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>28726</v>
+        <v>38955</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4662</v>
+        <v>-188933</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.1171</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>нет / нет</t>
+          <t>26810.33 / 268103.29</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
+          <t>Приморский край (точный адрес и график — в документации; в карточке не указаны)</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
+          <t>по 44-ФЗ — не более 7 раб. дн. после приёмки (проект контракта не приложен)</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
+          <t>в карточке графа нацрежима пустая — шины (22.11) обычно в ПП 1875 (ограничение) — проверить в документации; российские: КАМА (Нижнекамскшина), Cordiant, Алтайшина, Волтайр</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
-        </is>
-      </c>
-      <c r="R6" s="10" t="inlineStr">
-        <is>
-          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
+          <t>закрытая процедура ГОЗ: отдельный счёт в уполномоченном банке; антидемпинг при снижении ≥25%</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>Нужна документация (размеры, модели, сезонность, индекс нагрузки) — по оценке маржа ~15%, при −10% около +0,15 млн</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
+          <t>размеры шин неизвестны — военные/спец. шины (ИД-П284, КИ-115, ВИ-3) дороже и в дефиците; доставка ~4 т/25 м³ до Приморья (оценка 180 тыс., можно брать у дилеров КАМА во Владивостоке); аукцион ГОЗ — снижение до 20–30%; обеспечение контракта 268 тыс.</t>
         </is>
       </c>
     </row>
@@ -989,80 +989,80 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>260000141501024</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
+          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Управление ФСБ России по Республике Тыва (ИНН 1701032940)</t>
+          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Поставка изделий медицинского назначения (8 позиций: пластырь, скарификаторы, перчатки нит</t>
+          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>208172.52</v>
+        <v>283105.45</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-11-17 05:00 (GMT+4) = 04:00 МСК</t>
+          <t>2026-11-02 12:00</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>162824</v>
+        <v>221000</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.2178</v>
+        <v>0.2194</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>20852</v>
+        <v>28726</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3157</v>
+        <v>4662</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.2178</v>
+        <v>0.2194</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>не установлено (НМЦК &lt; 1 млн) / 20 817,25 ₽ (10%) — БГ (ст.45, п.13 документации) или деньги</t>
+          <t>нет / нет</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>г. Кызыл, ул. Дружбы, 42А; срок исполнения 01.01.2027–01.05.2027 (разово или партиями — в проекте контракта, не приложен)</t>
+          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
+          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>В карточке по всем 8 позициям графа нацрежима ПУСТАЯ (при этом перчатки/шприцы/иглы обычно входят в перечни ПП 1875) — проверить в документации; если ограничение есть — нужен российский товар с реестр</t>
+          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31); аккредитация на АСТ ГОЗ; РУ на медизделия; ТЗ/характеристики (объёмы шприцев, размеры бинта, фасовка) в карточке не указаны</t>
-        </is>
-      </c>
-      <c r="R7" s="11" t="inlineStr">
-        <is>
-          <t>Низкий приоритет / скорее не идти: прибыль ~21 тыс.₽ при −10% и ~3 тыс.₽ при −20%, безубыточность ~−22%. Подавать только</t>
+          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>Единицы измерения позиций 1, 2, 8 (пластырь «шт» 1 817 ₽, скарификатор «шт» 800 ₽, вата «уп» 296 ₽) без ТЗ непонятны — себестоимость по ним оценка; Нацрежим в карточке не заполнен — возможно, ограничение указано в документации (перчатки, шприцы); Маленький контракт — логистика до Кызыла и БГ съедают заметную долю; при раздельных партиях прибыль падает; Кызыл: только автодоставка, сроки ТК 10–20 дн</t>
+          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
         </is>
       </c>
     </row>
@@ -1072,80 +1072,80 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
+          <t>Управление ФСБ России по Республике Тыва (ИНН 1701032940)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
+          <t>Поставка изделий медицинского назначения (8 позиций: пластырь, скарификаторы, перчатки нит</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>58890</v>
+        <v>208172.52</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
+          <t>2026-11-17 05:00 (GMT+4) = 04:00 МСК</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>57140</v>
+        <v>162824</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.2178</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>-4139</v>
+        <v>20852</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-10028</v>
+        <v>3157</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.2178</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
+          <t>не установлено (НМЦК &lt; 1 млн) / 20 817,25 ₽ (10%) — БГ (ст.45, п.13 документации) или деньги</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
+          <t>г. Кызыл, ул. Дружбы, 42А; срок исполнения 01.01.2027–01.05.2027 (разово или партиями — в проекте контракта, не приложен)</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
+          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
+          <t>В карточке по всем 8 позициям графа нацрежима ПУСТАЯ (при этом перчатки/шприцы/иглы обычно входят в перечни ПП 1875) — проверить в документации; если ограничение есть — нужен российский товар с реестр</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
-        </is>
-      </c>
-      <c r="R8" s="9" t="inlineStr">
-        <is>
-          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
+          <t>ET44 (ч.1 ст.31); аккредитация на АСТ ГОЗ; РУ на медизделия; ТЗ/характеристики (объёмы шприцев, размеры бинта, фасовка) в карточке не указаны</t>
+        </is>
+      </c>
+      <c r="R8" s="11" t="inlineStr">
+        <is>
+          <t>Низкий приоритет / скорее не идти: прибыль ~21 тыс.₽ при −10% и ~3 тыс.₽ при −20%, безубыточность ~−22%. Подавать только</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
+          <t>Единицы измерения позиций 1, 2, 8 (пластырь «шт» 1 817 ₽, скарификатор «шт» 800 ₽, вата «уп» 296 ₽) без ТЗ непонятны — себестоимость по ним оценка; Нацрежим в карточке не заполнен — возможно, ограничение указано в документации (перчатки, шприцы); Маленький контракт — логистика до Кызыла и БГ съедают заметную долю; при раздельных партиях прибыль падает; Кызыл: только автодоставка, сроки ТК 10–20 дн</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0348100063126000025</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1165,60 +1165,70 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>УМВД России по г.о. Химки (ИНН 5047015587)</t>
+          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Оказание услуг по подготовке зданий и сооружений к отопительному сезону: подготовка систем</t>
+          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>312000</v>
+        <v>58890</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-11-09 11:00 МСК</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="8" t="n"/>
+          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>57140</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>-4139</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>-10028</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0.0297</v>
+      </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>не установлено (в карточке нет; НМЦК &lt; 1 млн) / 31 200 ₽ (10%), БГ или деньги</t>
+          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>Химки: ул. Гоголя, 4 (подвал, ИТП), ул. Гоголя, 6 (зд. «а» и «б»: подвал, 1 этаж ДЧ, архив, кабинеты, чердак), ул. Лавочкина, 12А, пр-т Мира, 23 «а», Вашутинское ш., 22Д; срок исполнения — до 31.12.2026</t>
+          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет 2026, КВР 244; порядок оплаты в проекте контракта (не приложен); по 44-ФЗ — не более 7 раб. дней с даты подписания документа о приё</t>
+          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Не указан (услуга)</t>
+          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31 44-ФЗ); TOVNPIVR (нет в РНП за отказ из-за санкций против заказчика); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
         </is>
       </c>
       <c r="R9" s="9" t="inlineStr">
         <is>
-          <t>Не идти — не наш профиль (услуги, нужна своя сантехническая бригада или субподрядчик); отопительный сезон уже идёт, срок</t>
+          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>Исполнение только через субподрядчика — маржа посредника на работах мала, ответственность за качество и сроки на нас; Приёмка работ по актам на режимном объекте МВД, допуск персонала; Обеспечение 31,2 тыс. ₽ и штрафы 44-ФЗ при узком сроке (до 31.12.2026)</t>
+          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
         </is>
       </c>
     </row>
@@ -1228,30 +1238,30 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0172400000226000017</t>
+          <t>0348100063126000025</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24); цена единицы — сумма цен единиц (ч.24 ст.22 44-ФЗ)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>ГУ Росгвардии по г. Санкт-Петербургу и Ленинградской области (ИНН 7842119240)</t>
+          <t>УМВД России по г.о. Химки (ИНН 5047015587)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Поставка запасных частей для ремонта военной и специальной техники в 2027 году (ОКПД2 29.3</t>
+          <t>Оказание услуг по подготовке зданий и сооружений к отопительному сезону: подготовка систем</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2000000</v>
+        <v>312000</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-11-13 09:00 МСК</t>
+          <t>2026-11-09 11:00 МСК</t>
         </is>
       </c>
       <c r="H10" s="7" t="n"/>
@@ -1261,37 +1271,37 @@
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>20 000 ₽ (1%) / 200 000 ₽ (10%) + обеспечение гарантийных обязательств 200 000 ₽ (10%)</t>
+          <t>не установлено (в карточке нет; НМЦК &lt; 1 млн) / 31 200 ₽ (10%), БГ или деньги</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>По адресу, указанному в заявке заказчика, в пределах Санкт-Петербурга, раб. дни 9:00–16:00 (обед 13–14); исполнение 01.01.2027–31.12.2027</t>
+          <t>Химки: ул. Гоголя, 4 (подвал, ИТП), ул. Гоголя, 6 (зд. «а» и «б»: подвал, 1 этаж ДЧ, архив, кабинеты, чердак), ул. Лавочкина, 12А, пр-т Мира, 23 «а», Вашутинское ш., 22Д; срок исполнения — до 31.12.2026</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Федеральный бюджет 2027 (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки каждой партии; гарантия — не менее заводской, а </t>
+          <t>Федеральный бюджет 2026, КВР 244; порядок оплаты в проекте контракта (не приложен); по 44-ФЗ — не более 7 раб. дней с даты подписания документа о приё</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>В карточке по позиции не указан (графа пустая) — проверить в извещении/ТЗ</t>
+          <t>Не указан (услуга)</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>ET44; TOVNPIVR; участник не под спецмерами Указа №252 и не под контролем таких лиц; ответственность за антиконкурентные соглашения; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+          <t>ET44 (ч.1 ст.31 44-ФЗ); TOVNPIVR (нет в РНП за отказ из-за санкций против заказчика); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
         </is>
       </c>
       <c r="R10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Не подавать вслепую — запросить ТЗ/обоснование НМЦК; решение после сверки цен единиц. Потенциально интересно (2 млн ₽ в </t>
+          <t>Не идти — не наш профиль (услуги, нужна своя сантехническая бригада или субподрядчик); отопительный сезон уже идёт, срок</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безубыточное снижение = средняя наценка цен единиц ТЗ над рынком; торг по сумме цен единиц часто уходит на 30–60%; Заказчик не обязан выбрать весь лимит 2 млн ₽ — выручка не гарантирована; Спецтехника (БТР, «Тайфун», «Тигр», Урал) — часть позиций только у заводов/дилеров, длинные сроки, возможен запрет аналогов; Сроки поставки по заявке (часы/дни) и штрафы — в проекте контракта; Заморозка 200+200 </t>
+          <t>Исполнение только через субподрядчика — маржа посредника на работах мала, ответственность за качество и сроки на нас; Приёмка работ по актам на режимном объекте МВД, допуск персонала; Обеспечение 31,2 тыс. ₽ и штрафы 44-ФЗ при узком сроке (до 31.12.2026)</t>
         </is>
       </c>
     </row>
@@ -1301,28 +1311,30 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>260003123900911</t>
+          <t>0172400000226000017</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, по итогам — договор)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24); цена единицы — сумма цен единиц (ч.24 ст.22 44-ФЗ)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>АО «ЦС «Звёздочка», филиал «35 СРЗ», Мурманск, ул. Адмирала флота Лобова, 100 (И</t>
+          <t>ГУ Росгвардии по г. Санкт-Петербургу и Ленинградской области (ИНН 7842119240)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Вооружение рукава 511-77.012 — 6 шт (ОКПД2 22.19.30.139), ГОЗ</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n"/>
+          <t>Поставка запасных частей для ремонта военной и специальной техники в 2027 году (ОКПД2 29.3</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>2000000</v>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-11-03 08:00</t>
+          <t>2026-11-13 09:00 МСК</t>
         </is>
       </c>
       <c r="H11" s="7" t="n"/>
@@ -1332,35 +1344,106 @@
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
+          <t>20 000 ₽ (1%) / 200 000 ₽ (10%) + обеспечение гарантийных обязательств 200 000 ₽ (10%)</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>По адресу, указанному в заявке заказчика, в пределах Санкт-Петербурга, раб. дни 9:00–16:00 (обед 13–14); исполнение 01.01.2027–31.12.2027</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Федеральный бюджет 2027 (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки каждой партии; гарантия — не менее заводской, а </t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>В карточке по позиции не указан (графа пустая) — проверить в извещении/ТЗ</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>ET44; TOVNPIVR; участник не под спецмерами Указа №252 и не под контролем таких лиц; ответственность за антиконкурентные соглашения; Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Не подавать вслепую — запросить ТЗ/обоснование НМЦК; решение после сверки цен единиц. Потенциально интересно (2 млн ₽ в </t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Безубыточное снижение = средняя наценка цен единиц ТЗ над рынком; торг по сумме цен единиц часто уходит на 30–60%; Заказчик не обязан выбрать весь лимит 2 млн ₽ — выручка не гарантирована; Спецтехника (БТР, «Тайфун», «Тигр», Урал) — часть позиций только у заводов/дилеров, длинные сроки, возможен запрет аналогов; Сроки поставки по заявке (часы/дни) и штрафы — в проекте контракта; Заморозка 200+200 </t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>260003123900911</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, по итогам — договор)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>АО «ЦС «Звёздочка», филиал «35 СРЗ», Мурманск, ул. Адмирала флота Лобова, 100 (И</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Вооружение рукава 511-77.012 — 6 шт (ОКПД2 22.19.30.139), ГОЗ</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-03 08:00</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
           <t>нет / нет</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>До терминала транспортной компании в г. Мурманске в течение 30 к.д. с даты получения 100% оплаты (в тексте «силами и за счёт средств Покупателя» — уточнить, кто оплачивает перевозку до Мурманска)</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>100% предоплата в течение 30 к.д. с момента получения счёта, с отдельного счёта Покупателя в ПАО «Банк ПСБ», ИГК 1619187304551432209007007 → у нас нуж</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>В карточке лота — запрет закупок иностранных товаров; в Заявке.docx — запреты/ограничения/преимущество ПП 1875 НЕ применяются (абз.3 пп.«и» п.4) — противоречие, уточнить. Аналог не допускается; указан</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Счёт/КП в составе заявки; товар 2026 г. выпуска, новый, заводская упаковка; паспорта/сертификаты; документация на русском по ГОСТ Р 2.601-2019, 2.610-2019 с учётом ГОСТ РВ 0002-601-2019; РКД на изготовление поставщик приобретает за свой счёт у КБ-держателя; ГОЗ: отдельный счёт, раздельный учёт</t>
         </is>
       </c>
-      <c r="R11" s="9" t="inlineStr">
+      <c r="R12" s="9" t="inlineStr">
         <is>
           <t>Не идти без расшифровки — срочно (до 03.11) запросить у заказчика параметры изделия; идти только при найденном изготовит</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>Позиция не расшифрована: что запросить — чертёж/параметры 511-77.012 (тип рукава, DN, PN, длина, среда, тип и материал арматуры, ГОСТ/ОСТ), держатель КД (КБ), прежние поставщики и цены, вид приёмки (ОТК/ВП МО), требования к консервации и упаковке, кто платит доставку до Мурманска; Покупка РКД у КБ за наш счёт — для посредника почти нереально в 5 дней; ГОЗ: отдельный счёт в уполномоченном банке, ра</t>
         </is>
@@ -1378,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2864,535 +2947,977 @@
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
+          <t>Шина пневм. для легкового автомобиля</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E44" s="14" t="n">
-        <v>514.74</v>
+        <v>9000</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>380</v>
+        <v>7000</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>0.2617632202665423</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>1. Лейкопластырь для поверхностных ран</t>
+          <t>Шина пневм. для легкового автомобиля</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E45" s="14" t="n">
-        <v>1816.67</v>
+        <v>10100</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1300</v>
+        <v>8000</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>0.284404982743151</v>
+        <v>0.2079207920792079</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>оценка: «шт» за 1 816,67 ₽ — вероятно упаковка/рулон (ТЗ нет); бактерицидные/фиксирующие пластыри рос. производства (Верофарм, Мирал, Медрулон) — оценка 70% НМЦ</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2. Ручка-скарификатор автоматическая, одноразового использования</t>
+          <t>Шина пневм. для легкового автомобиля</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E46" s="14" t="n">
-        <v>800</v>
+        <v>12066.66</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>560</v>
+        <v>9500</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>0.3</v>
+        <v>0.2127067473517941</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>оценка: 800 ₽ за «шт» — скорее упаковка ланцетов/скарификаторов-ручек (ТЗ нет); безопасные ланцеты 100 шт в опте ~500–700 ₽ — оценка, единица измерения требует проверки</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>3. Перчатки смотровые/процедурные нитриловые, неопудренные, нестерильные</t>
+          <t>Шина пневм. для легкового автомобиля</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>8000</v>
+        <v>4</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Пара (2 шт.)</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E47" s="14" t="n">
-        <v>10.34</v>
+        <v>16166.66</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>7</v>
+        <v>13000</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>0.3230174081237911</v>
+        <v>0.1958759570622504</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Webpack: нитрил смотр. неопудр. 100 шт (50 пар) 400 ₽, опт от 69 уп. 350 ₽ → 7,0 ₽/пара https://webpack.ru/sredstva-individyalnoiy-zashitu/perchatki/perchatki-nitrilovye/ ; Trial Market ~390 ₽/100 шт</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>4. Шприц общего назначения</t>
+          <t>Шина пневм. для легкового автомобиля</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4000</v>
+        <v>26</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E48" s="14" t="n">
-        <v>5.5</v>
+        <v>10466.66</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>3.8</v>
+        <v>8200</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>0.3090909090909091</v>
+        <v>0.2165600105477774</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>НВ-Лаб: шприц 5 мл 3-комп. опт 3 ₽, розн. 4 ₽ https://www.nv-lab.ru/catalog_info.php?ID=6920 ; российский (Медполимер/СФМ) — оценка 3,8 ₽; объём шприца в карточке не указан (по цене 5,5 ₽ — 2–5 мл)</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>5. Игла для забора крови, стандартная</t>
+          <t>Шина пневм. для автобусов</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E49" s="14" t="n">
-        <v>19.33</v>
+        <v>6766.66</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>4.22</v>
+        <v>5500</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>0.7816864976720124</v>
+        <v>0.1871913174298694</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Sunmed: игла двусторонняя 21G «ЕЛАМЕД» (РФ) 8516 — 4,22 ₽ опт, цена на 14.04.2026 https://www.sunmed.ru/product/igla-dvustoronnyaya-dlya-vakuumnoy-sistemy-zabora-krovi-elamed-8516/</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>6. Бинт эластичный, нелатексный, нестерильный, одноразового использования</t>
+          <t>Шина пневм. для автобусов</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>315.67</v>
+        <v>7766.66</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>265</v>
+        <v>6300</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>0.1605157284505971</v>
+        <v>0.188840505442494</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Комета-мед: бинт эласт. компрессионный 10 см×5 м Медитек — 295 ₽ https://kometa-med.com/product/bint-elastichnyj-kompressionnyj-meditek-sr-10-sm-h-5-m/ −10% торг ≈ 265 ₽; размер в карточке не указан</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>7. Шприц общего назначения</t>
+          <t>Шина пневм. для автобусов</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E51" s="14" t="n">
-        <v>12.34</v>
+        <v>9433.33</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>7.1</v>
+        <v>7600</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>0.4246353322528363</v>
+        <v>0.1943460050692597</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>оптовый прайс: шприц 3-комп. 20 мл — 7,90 ₽ (поиск по шприцевым оптовикам), другой магазин 5,10 ₽/шт (уп.100) → 7,1 ₽ после торга; объём в карточке не указан (10–20 мл)</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>8. Ватные шарики</t>
+          <t>Шина пневм. для автобусов</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Упаковка</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>296.34</v>
+        <v>7766.66</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>180</v>
+        <v>6300</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>0.3925895930350273</v>
+        <v>0.188840505442494</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>оценка: «упаковка» без фасовки (ТЗ нет); шарики ватные нестерильные 100–200 шт/уп рос. пр-ва (Емельянъ Савостинъ, Амелия) — оценка 60% НМЦ</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
+          <t>Шина пневм. для грузовых автомобилей</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E53" s="14" t="n">
-        <v>14400</v>
+        <v>41333.33</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>11580</v>
+        <v>34000</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>0.1958333333333333</v>
+        <v>0.1774192885015555</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
+          <t>Шина пневм. для грузовых автомобилей</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E54" s="14" t="n">
-        <v>792</v>
+        <v>37000</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>900</v>
+        <v>30000</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>-0.1363636363636365</v>
+        <v>0.1891891891891891</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Песок (строительный, по ТЗ)</t>
+          <t>Шина пневм. для грузовых автомобилей</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E55" s="14" t="n">
-        <v>654</v>
+        <v>70333.33</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>990</v>
+        <v>60000</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>-0.5137614678899083</v>
+        <v>0.1469193908492602</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
+          <t>Шина пневм. для грузовых автомобилей</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>п.м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
-        <v>300</v>
+        <v>55666.66</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>200</v>
+        <v>47000</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.155688521639344</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
+          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
         </is>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>0348100063126000025</t>
+          <t>260000141501024</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Работы/услуги по подготовке системы отопления к сезону и ППР (промывка/опрессовка, обслуживание ИТП и т.п. — состав в ТЗ</t>
+          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>усл. ед.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="E57" s="14" t="n">
-        <v>312000</v>
-      </c>
-      <c r="F57" s="14" t="n"/>
-      <c r="G57" s="15" t="n"/>
+        <v>514.74</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>0.2617632202665423</v>
+      </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>Себестоимость не оценивалась: это работы (персонал-сантехники, оборудование для промывки/опрессовки, допуск на объекты МВД), не поставка товара</t>
+          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
         </is>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>0172400000226000017</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>Запчасти для ремонта ВиСТ — перечень в ТЗ (в карточке одна обобщённая позиция)</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>по заявкам до исчерпания 2 000 000 ₽</t>
-        </is>
+          <t>1. Лейкопластырь для поверхностных ран</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="14" t="n"/>
-      <c r="G58" s="15" t="n"/>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>1816.67</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>0.284404982743151</v>
+      </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">«Цена за единицу» 6 458 937 848,97 ₽ — это не цена товара, а СУММА начальных цен единиц всех позиций каталога (ч.24 ст.22 44-ФЗ: количество заранее не определено). Торг идёт по снижению этой суммы; контракт заключается на максимальное значение 2 000 </t>
+          <t>оценка: «шт» за 1 816,67 ₽ — вероятно упаковка/рулон (ТЗ нет); бактерицидные/фиксирующие пластыри рос. производства (Верофарм, Мирал, Медрулон) — оценка 70% НМЦ</t>
         </is>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
         <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>2. Ручка-скарификатор автоматическая, одноразового использования</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>оценка: 800 ₽ за «шт» — скорее упаковка ланцетов/скарификаторов-ручек (ТЗ нет); безопасные ланцеты 100 шт в опте ~500–700 ₽ — оценка, единица измерения требует проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>3. Перчатки смотровые/процедурные нитриловые, неопудренные, нестерильные</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Пара (2 шт.)</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" s="15" t="n">
+        <v>0.3230174081237911</v>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>Webpack: нитрил смотр. неопудр. 100 шт (50 пар) 400 ₽, опт от 69 уп. 350 ₽ → 7,0 ₽/пара https://webpack.ru/sredstva-individyalnoiy-zashitu/perchatki/perchatki-nitrilovye/ ; Trial Market ~390 ₽/100 шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>4. Шприц общего назначения</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G61" s="15" t="n">
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>НВ-Лаб: шприц 5 мл 3-комп. опт 3 ₽, розн. 4 ₽ https://www.nv-lab.ru/catalog_info.php?ID=6920 ; российский (Медполимер/СФМ) — оценка 3,8 ₽; объём шприца в карточке не указан (по цене 5,5 ₽ — 2–5 мл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>5. Игла для забора крови, стандартная</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>0.7816864976720124</v>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>Sunmed: игла двусторонняя 21G «ЕЛАМЕД» (РФ) 8516 — 4,22 ₽ опт, цена на 14.04.2026 https://www.sunmed.ru/product/igla-dvustoronnyaya-dlya-vakuumnoy-sistemy-zabora-krovi-elamed-8516/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>6. Бинт эластичный, нелатексный, нестерильный, одноразового использования</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>315.67</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>265</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>0.1605157284505971</v>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>Комета-мед: бинт эласт. компрессионный 10 см×5 м Медитек — 295 ₽ https://kometa-med.com/product/bint-elastichnyj-kompressionnyj-meditek-sr-10-sm-h-5-m/ −10% торг ≈ 265 ₽; размер в карточке не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>7. Шприц общего назначения</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>0.4246353322528363</v>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>оптовый прайс: шприц 3-комп. 20 мл — 7,90 ₽ (поиск по шприцевым оптовикам), другой магазин 5,10 ₽/шт (уп.100) → 7,1 ₽ после торга; объём в карточке не указан (10–20 мл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>0312100011426000102</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>8. Ватные шарики</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Упаковка</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="G65" s="15" t="n">
+        <v>0.3925895930350273</v>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>оценка: «упаковка» без фасовки (ТЗ нет); шарики ватные нестерильные 100–200 шт/уп рос. пр-ва (Емельянъ Савостинъ, Амелия) — оценка 60% НМЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>11580</v>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>0.1958333333333333</v>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>792</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="G67" s="15" t="n">
+        <v>-0.1363636363636365</v>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Песок (строительный, по ТЗ)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>654</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>990</v>
+      </c>
+      <c r="G68" s="15" t="n">
+        <v>-0.5137614678899083</v>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>0362100023526000014</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>п.м</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G69" s="15" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>0348100063126000025</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Работы/услуги по подготовке системы отопления к сезону и ППР (промывка/опрессовка, обслуживание ИТП и т.п. — состав в ТЗ</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>312000</v>
+      </c>
+      <c r="F70" s="14" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>Себестоимость не оценивалась: это работы (персонал-сантехники, оборудование для промывки/опрессовки, допуск на объекты МВД), не поставка товара</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>0172400000226000017</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Запчасти для ремонта ВиСТ — перечень в ТЗ (в карточке одна обобщённая позиция)</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>по заявкам до исчерпания 2 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="n"/>
+      <c r="F71" s="14" t="n"/>
+      <c r="G71" s="15" t="n"/>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">«Цена за единицу» 6 458 937 848,97 ₽ — это не цена товара, а СУММА начальных цен единиц всех позиций каталога (ч.24 ст.22 44-ФЗ: количество заранее не определено). Торг идёт по снижению этой суммы; контракт заключается на максимальное значение 2 000 </t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
           <t>260003123900911</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>Вооружение рукава (рукав с концевой арматурой) по обозначению 511-77.012</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C72" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="15" t="n"/>
-      <c r="H59" s="13" t="inlineStr">
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>НМЦ не указана (0,00) — цену формирует наше КП. Себестоимость определить нельзя: изделие изготавливается по чертежу 511-77.012 (судостроительная КД), рыночной цены нет. Метод: запрос КП у изготовителей рукавов по КД (РВД/металлорукава для флота) посл</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/GOZ_2910.xlsx
+++ b/GOZ_2910.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>Нужна документация (размеры, модели, сезонность, индекс нагрузки) — по оценке маржа ~15%, при −10% около +0,15 млн</t>
+          <t>Без ТЗ не идти: по оценке маржа ~12% при НМЦК, при −10% всего ~+39 тыс., при −20% убыток ~−189 тыс.; нужны размеры/модел</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">

--- a/GOZ_2910.xlsx
+++ b/GOZ_2910.xlsx
@@ -906,80 +906,80 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>260000141501024</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион 44-ФЗ</t>
+          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Пограничное управление ФСБ России по Приморскому краю</t>
+          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Шины пневматические (ГОЗ, ГПВ): 13 позиций — легковые 99 шт, для автобусов 28 шт, грузовые</t>
+          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2681032.86</v>
+        <v>283105.45</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>16.11.2026 02:45 (GMT+4) = 01:45 МСК</t>
+          <t>2026-11-02 12:00</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>2367100</v>
+        <v>221000</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1171</v>
+        <v>0.2194</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>38955</v>
+        <v>28726</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-188933</v>
+        <v>4662</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.1171</v>
+        <v>0.2194</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>26810.33 / 268103.29</t>
+          <t>нет / нет</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Приморский край (точный адрес и график — в документации; в карточке не указаны)</t>
+          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>по 44-ФЗ — не более 7 раб. дн. после приёмки (проект контракта не приложен)</t>
+          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>в карточке графа нацрежима пустая — шины (22.11) обычно в ПП 1875 (ограничение) — проверить в документации; российские: КАМА (Нижнекамскшина), Cordiant, Алтайшина, Волтайр</t>
+          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>закрытая процедура ГОЗ: отдельный счёт в уполномоченном банке; антидемпинг при снижении ≥25%</t>
-        </is>
-      </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>Без ТЗ не идти: по оценке маржа ~12% при НМЦК, при −10% всего ~+39 тыс., при −20% убыток ~−189 тыс.; нужны размеры/модел</t>
+          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>размеры шин неизвестны — военные/спец. шины (ИД-П284, КИ-115, ВИ-3) дороже и в дефиците; доставка ~4 т/25 м³ до Приморья (оценка 180 тыс., можно брать у дилеров КАМА во Владивостоке); аукцион ГОЗ — снижение до 20–30%; обеспечение контракта 268 тыс.</t>
+          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
         </is>
       </c>
     </row>
@@ -989,80 +989,80 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>закупка малого объёма 223-ФЗ на АСТ ГОЗ (ГОЗ, ГК № Н/1/2/0428/ГК-19-ДГОЗ от 04.12.2019)</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>АО «ЦС «Звёздочка», Северодвинск, пр-д Машиностроителей, 12 (ИНН 2902060361); за</t>
+          <t>Управление ФСБ России по Республике Тыва (ИНН 1701032940)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Кабель (провод) ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014 — 550 м (ОКПД2 27.32.13.1</t>
+          <t>Поставка изделий медицинского назначения (8 позиций: пластырь, скарификаторы, перчатки нит</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>283105.45</v>
+        <v>208172.52</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00</t>
+          <t>2026-11-17 05:00 (GMT+4) = 04:00 МСК</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>221000</v>
+        <v>162824</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.2178</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>28726</v>
+        <v>20852</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>4662</v>
+        <v>3157</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.2178</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>нет / нет</t>
+          <t>не установлено (НМЦК &lt; 1 млн) / 20 817,25 ₽ (10%) — БГ (ст.45, п.13 документации) или деньги</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>Силами и средствами Поставщика на склад Покупателя: Архангельская обл., г. Северодвинск, пр. Машиностроителей, д. 12 (склад 112), в течение 30 рабочих дней с момента 100% предоплаты</t>
+          <t>г. Кызыл, ул. Дружбы, 42А; срок исполнения 01.01.2027–01.05.2027 (разово или партиями — в проекте контракта, не приложен)</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>100% предоплата в течение 10 раб. дней с даты решения о проведении МЗ при условии поступления денег от Основного заказчика; НМЦ 283 105,45 ₽ в т.ч. НД</t>
+          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Исключение по пп.«и» п.5 ПП 1875 — запрет/ограничение не применяются; аналог не допускается (только по ТУ BY 500017371.075-2014, белорусский производитель)</t>
+          <t>В карточке по всем 8 позициям графа нацрежима ПУСТАЯ (при этом перчатки/шприцы/иглы обычно входят в перечни ПП 1875) — проверить в документации; если ограничение есть — нужен российский товар с реестр</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Счёт по «Требованиям к оформлению счетов»: реквизиты, «без НДС (УСН)», срок действия ≥60 к.д., срок/условия оплаты и поставки, гарантии и условия поставки по ТУ BY, номер ГК Н/1/2/0428/ГК-19-ДГОЗ, вид приёмки ОТК, печать/подпись; товар новый, не складского хранения; паспорт, сертификат качества; ГОЗ</t>
-        </is>
-      </c>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>Идти — при подтверждённом КП на кабель именно по ТУ BY 500017371.075-2014 (не по ГОСТ/ТУ РФ); цена −5…−10% от НМЦ даёт ~</t>
+          <t>ET44 (ч.1 ст.31); аккредитация на АСТ ГОЗ; РУ на медизделия; ТЗ/характеристики (объёмы шприцев, размеры бинта, фасовка) в карточке не указаны</t>
+        </is>
+      </c>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>Низкий приоритет / скорее не идти: прибыль ~21 тыс.₽ при −10% и ~3 тыс.₽ при −20%, безубыточность ~−22%. Подавать только</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>Аналог не допускается: нужен товар строго по ТУ BY 500017371.075-2014, с паспортом/сертификатом; кабель РФ по ГОСТ отклонят; «Не складского хранения» — нужна свежая партия с завода; Предоплата только «при поступлении средств от Основного заказчика» — срок оплаты может сдвинуться; ГОЗ: отдельный счёт по ИГК в уполномоченном банке, раздельный учёт, ограничения оплаты поставщику и вывода прибыли; Есл</t>
+          <t>Единицы измерения позиций 1, 2, 8 (пластырь «шт» 1 817 ₽, скарификатор «шт» 800 ₽, вата «уп» 296 ₽) без ТЗ непонятны — себестоимость по ним оценка; Нацрежим в карточке не заполнен — возможно, ограничение указано в документации (перчатки, шприцы); Маленький контракт — логистика до Кызыла и БГ съедают заметную долю; при раздельных партиях прибыль падает; Кызыл: только автодоставка, сроки ТК 10–20 дн</t>
         </is>
       </c>
     </row>
@@ -1072,80 +1072,80 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. «а»,«б»,«г» п.5 ч.11 ст.24), АСТ ГОЗ</t>
+          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Управление ФСБ России по Республике Тыва (ИНН 1701032940)</t>
+          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Поставка изделий медицинского назначения (8 позиций: пластырь, скарификаторы, перчатки нит</t>
+          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>208172.52</v>
+        <v>58890</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-11-17 05:00 (GMT+4) = 04:00 МСК</t>
+          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>162824</v>
+        <v>57140</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.2178</v>
+        <v>0.0297</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>20852</v>
+        <v>-4139</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>3157</v>
+        <v>-10028</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.2178</v>
+        <v>0.0297</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>не установлено (НМЦК &lt; 1 млн) / 20 817,25 ₽ (10%) — БГ (ст.45, п.13 документации) или деньги</t>
+          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>г. Кызыл, ул. Дружбы, 42А; срок исполнения 01.01.2027–01.05.2027 (разово или партиями — в проекте контракта, не приложен)</t>
+          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет 2027, КВР 244; срок — в проекте контракта; по 44-ФЗ не более 7 раб. дней с подписания документа о приёмке</t>
+          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>В карточке по всем 8 позициям графа нацрежима ПУСТАЯ (при этом перчатки/шприцы/иглы обычно входят в перечни ПП 1875) — проверить в документации; если ограничение есть — нужен российский товар с реестр</t>
+          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31); аккредитация на АСТ ГОЗ; РУ на медизделия; ТЗ/характеристики (объёмы шприцев, размеры бинта, фасовка) в карточке не указаны</t>
-        </is>
-      </c>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>Низкий приоритет / скорее не идти: прибыль ~21 тыс.₽ при −10% и ~3 тыс.₽ при −20%, безубыточность ~−22%. Подавать только</t>
+          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>Единицы измерения позиций 1, 2, 8 (пластырь «шт» 1 817 ₽, скарификатор «шт» 800 ₽, вата «уп» 296 ₽) без ТЗ непонятны — себестоимость по ним оценка; Нацрежим в карточке не заполнен — возможно, ограничение указано в документации (перчатки, шприцы); Маленький контракт — логистика до Кызыла и БГ съедают заметную долю; при раздельных партиях прибыль падает; Кызыл: только автодоставка, сроки ТК 10–20 дн</t>
+          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
         </is>
       </c>
     </row>
@@ -1155,80 +1155,80 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>закрытый аукцион в электронной форме 44-ФЗ (пп. а,б,г п.5 ч.11 ст.24)</t>
+          <t>закрытый аукцион 44-ФЗ</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Войсковая часть 3732 (Росгвардия), Екатеринбург, ул. Фрунзе, 74А (ИНН 6664015460</t>
+          <t>Пограничное управление ФСБ России по Приморскому краю</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Поставка строительных материалов: портландцемент 0,5 т, щебень 15 м3, песок 15 м3, труба с</t>
+          <t>Шины пневматические (ГОЗ, ГПВ): 13 позиций — легковые 99 шт, для автобусов 28 шт, грузовые</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>58890</v>
+        <v>2681032.86</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-11-11 09:00 (GMT+5) = 07:00 МСК</t>
+          <t>16.11.2026 02:45 (GMT+4) = 01:45 МСК</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>57140</v>
+        <v>2471998.88</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.078</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>-4139</v>
+        <v>-59069.31</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-10028</v>
+        <v>-327172.59</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.078</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>не установлено (в карточке нет) / 5 889 ₽ (10%)</t>
+          <t>26810.33 / 268103.29</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>г.о. Екатеринбург, точный адрес — в извещении/ТЗ (не приложены); срок исполнения 01.01.2027–30.04.2027</t>
+          <t>Приморский край (точный адрес и график — в документации; в карточке не указаны)</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Федеральный бюджет, деньги 2027 г. (первый плановый год), КВР 244; по 44-ФЗ — не более 7 раб. дней после приёмки; гарантия — «указан в заявке на закуп</t>
+          <t>по 44-ФЗ — не более 7 раб. дн. после приёмки (проект контракта не приложен)</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ПП 1875: цемент и щебень — ограничение (Прил. 2: при наличии заявки с российским товаром иностранные отклоняются; нужен номер реестровой записи ГИСП); песок и труба — преимущество (Прил. 3)</t>
+          <t>в карточке графа нацрежима пустая — шины (22.11) обычно в ПП 1875 (ограничение) — проверить в документации; российские: КАМА (Нижнекамскшина), Cordiant, Алтайшина, Волтайр</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>ET44 (ч.1 ст.31 44-ФЗ); Аккредитация на АСТ ГОЗ для закрытых процедур; документация (ТЗ, проект контракта) доступна только аккредитованным участникам — в присланной карточке её нет; номер реестровой записи на цемент/щебень у производителя</t>
+          <t>закрытая процедура ГОЗ: отдельный счёт в уполномоченном банке; антидемпинг при снижении ≥25%</t>
         </is>
       </c>
       <c r="R9" s="9" t="inlineStr">
         <is>
-          <t>Не идти — щебень и песок в НМЦ ниже рынка с доставкой, общая маржа ~3% при НМЦК, любое снижение — убыток; сумма мизерная</t>
+          <t>Не идти по рознице: безубыточно ~8% (опт −10% — ~13%); идти только с оптовым КП (ГРУЗШИНА, Приморская шинная, ТД КАМА) и</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>Размер трубы и фракции не известны без ТЗ — при трубе большего диаметра убыток растёт; Цемент/щебень под ограничением ПП 1875 — нужна реестровая запись ГИСП, иначе отклонение; Поставка в январе–апреле 2027: зимний завоз нерудных, рост цен 2027; Выручка 58 тыс. ₽ не покрывает затрат на участие</t>
+          <t>размеры шин неизвестны — военные/спец. шины (ИД-П284, КИ-115, ВИ-3) дороже и в дефиците; доставка ~4 т/25 м³ до Приморья (оценка 180 тыс., можно брать у дилеров КАМА во Владивостоке); аукцион ГОЗ — снижение до 20–30%; обеспечение контракта 268 тыс.; размеры — предположение по цене; НМЦ ≈ розница Владивостока</t>
         </is>
       </c>
     </row>
@@ -2947,884 +2947,884 @@
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>260000141501024</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для легкового автомобиля</t>
+          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>60</v>
+        <v>550</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="E44" s="14" t="n">
-        <v>9000</v>
+        <v>514.74</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>7000</v>
+        <v>380</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2617632202665423</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
         </is>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для легкового автомобиля</t>
+          <t>1. Лейкопластырь для поверхностных ран</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E45" s="14" t="n">
-        <v>10100</v>
+        <v>1816.67</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>8000</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>0.2079207920792079</v>
+        <v>0.284404982743151</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка: «шт» за 1 816,67 ₽ — вероятно упаковка/рулон (ТЗ нет); бактерицидные/фиксирующие пластыри рос. производства (Верофарм, Мирал, Медрулон) — оценка 70% НМЦ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для легкового автомобиля</t>
+          <t>2. Ручка-скарификатор автоматическая, одноразового использования</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E46" s="14" t="n">
-        <v>12066.66</v>
+        <v>800</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>9500</v>
+        <v>560</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>0.2127067473517941</v>
+        <v>0.3</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка: 800 ₽ за «шт» — скорее упаковка ланцетов/скарификаторов-ручек (ТЗ нет); безопасные ланцеты 100 шт в опте ~500–700 ₽ — оценка, единица измерения требует проверки</t>
         </is>
       </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для легкового автомобиля</t>
+          <t>3. Перчатки смотровые/процедурные нитриловые, неопудренные, нестерильные</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>8000</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Пара (2 шт.)</t>
         </is>
       </c>
       <c r="E47" s="14" t="n">
-        <v>16166.66</v>
+        <v>10.34</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>13000</v>
+        <v>7</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>0.1958759570622504</v>
+        <v>0.3230174081237911</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>Webpack: нитрил смотр. неопудр. 100 шт (50 пар) 400 ₽, опт от 69 уп. 350 ₽ → 7,0 ₽/пара https://webpack.ru/sredstva-individyalnoiy-zashitu/perchatki/perchatki-nitrilovye/ ; Trial Market ~390 ₽/100 шт</t>
         </is>
       </c>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для легкового автомобиля</t>
+          <t>4. Шприц общего назначения</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>26</v>
+        <v>4000</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E48" s="14" t="n">
-        <v>10466.66</v>
+        <v>5.5</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>8200</v>
+        <v>3.8</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>0.2165600105477774</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>НВ-Лаб: шприц 5 мл 3-комп. опт 3 ₽, розн. 4 ₽ https://www.nv-lab.ru/catalog_info.php?ID=6920 ; российский (Медполимер/СФМ) — оценка 3,8 ₽; объём шприца в карточке не указан (по цене 5,5 ₽ — 2–5 мл)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для автобусов</t>
+          <t>5. Игла для забора крови, стандартная</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E49" s="14" t="n">
-        <v>6766.66</v>
+        <v>19.33</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>5500</v>
+        <v>4.22</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>0.1871913174298694</v>
+        <v>0.7816864976720124</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>Sunmed: игла двусторонняя 21G «ЕЛАМЕД» (РФ) 8516 — 4,22 ₽ опт, цена на 14.04.2026 https://www.sunmed.ru/product/igla-dvustoronnyaya-dlya-vakuumnoy-sistemy-zabora-krovi-elamed-8516/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для автобусов</t>
+          <t>6. Бинт эластичный, нелатексный, нестерильный, одноразового использования</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>7766.66</v>
+        <v>315.67</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>6300</v>
+        <v>265</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>0.188840505442494</v>
+        <v>0.1605157284505971</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>Комета-мед: бинт эласт. компрессионный 10 см×5 м Медитек — 295 ₽ https://kometa-med.com/product/bint-elastichnyj-kompressionnyj-meditek-sr-10-sm-h-5-m/ −10% торг ≈ 265 ₽; размер в карточке не указан</t>
         </is>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для автобусов</t>
+          <t>7. Шприц общего назначения</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="E51" s="14" t="n">
-        <v>9433.33</v>
+        <v>12.34</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>7600</v>
+        <v>7.1</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>0.1943460050692597</v>
+        <v>0.4246353322528363</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оптовый прайс: шприц 3-комп. 20 мл — 7,90 ₽ (поиск по шприцевым оптовикам), другой магазин 5,10 ₽/шт (уп.100) → 7,1 ₽ после торга; объём в карточке не указан (10–20 мл)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0312100011426000102</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для автобусов</t>
+          <t>8. Ватные шарики</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>Упаковка</t>
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>7766.66</v>
+        <v>296.34</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>6300</v>
+        <v>180</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>0.188840505442494</v>
+        <v>0.3925895930350273</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка: «упаковка» без фасовки (ТЗ нет); шарики ватные нестерильные 100–200 шт/уп рос. пр-ва (Емельянъ Савостинъ, Амелия) — оценка 60% НМЦ</t>
         </is>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для грузовых автомобилей</t>
+          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>т</t>
         </is>
       </c>
       <c r="E53" s="14" t="n">
-        <v>41333.33</v>
+        <v>14400</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>34000</v>
+        <v>11580</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>0.1774192885015555</v>
+        <v>0.1958333333333333</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для грузовых автомобилей</t>
+          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E54" s="14" t="n">
-        <v>37000</v>
+        <v>792</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>30000</v>
+        <v>900</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>0.1891891891891891</v>
+        <v>-0.1363636363636365</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
         </is>
       </c>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для грузовых автомобилей</t>
+          <t>Песок (строительный, по ТЗ)</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E55" s="14" t="n">
-        <v>70333.33</v>
+        <v>654</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>60000</v>
+        <v>990</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>0.1469193908492602</v>
+        <v>-0.5137614678899083</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
         </is>
       </c>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>0320100031626000249</t>
+          <t>0362100023526000014</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Шина пневм. для грузовых автомобилей</t>
+          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>п.м</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
-        <v>55666.66</v>
+        <v>300</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>47000</v>
+        <v>200</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>0.155688521639344</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>ОЦЕНКА без ТЗ: размер/модель в карточке не указаны; принято ≈80–85% НМЦ за ед. по ценовому диапазону (легк. 9–16 тыс. ≈ УАЗ/внедорожные R16 КАМА/Cordiant; автобус 6,8–9,4 тыс. ≈ ГАЗель C-шины; груз. 37–70 тыс. ≈ КАМАЗ 425/85R21, 1220×400-533, 14.00-2</t>
+          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
         </is>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>260000141501024</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Кабель ПуГВнг(А)-LS 1×25 белый ТУ BY 500017371.075-2014</t>
+          <t>225/75R16 (УАЗ Патриот/Хантер) всесезон/лето КАМА-219; альт. 245/70R16 Cordiant All-Terrain (Патриот 2015+) — КАМА-219 2</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E57" s="14" t="n">
-        <v>514.74</v>
+        <v>9000</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>380</v>
+        <v>8740</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>0.2617632202665423</v>
+        <v>0.02888888888888885</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>оценка 380 ₽/м с НДС: рынок РФ ПуГВнг(А)-LS 1×25 белый 323–374 ₽/м (ЭТМ 323,34 ₽ барабан / 363 ₽ розница; Энергосфера 331; Вольткин 340; Кабель Иркутск 374) + надбавка за конкретный белорусский ТУ/ввоз из РБ: https://www.etm.ru/cat/nn/4813960 ; https</t>
+          <t>ГРУЗШИНА (UNITYRE) Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/225-75r16-kama-nizhnekamskij-shinnyj-zavod-219-rossija-letnie-legkovye-shiny-rovl20-g18348465118.html</t>
         </is>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>1. Лейкопластырь для поверхностных ран</t>
+          <t>235/75R15 (УАЗ Хантер/«буханка») Cordiant All-Terrain / Off Road 2 — Cordiant All-Terrain 235/75R15 109S</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E58" s="14" t="n">
-        <v>1816.67</v>
+        <v>10100</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>1300</v>
+        <v>8949</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>0.284404982743151</v>
+        <v>0.113960396039604</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>оценка: «шт» за 1 816,67 ₽ — вероятно упаковка/рулон (ТЗ нет); бактерицидные/фиксирующие пластыри рос. производства (Верофарм, Мирал, Медрулон) — оценка 70% НМЦ</t>
+          <t>Шинсервис Владивосток: https://vladivostok.shinservice.ru/catalog/cordiant/summer/cordiant_all_terrain/235-75-R15/109S/?idx=812532</t>
         </is>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>2. Ручка-скарификатор автоматическая, одноразового использования</t>
+          <t>245/70R16 зимняя шип. Cordiant Snow Cross 2 SUV; альт. M/T Cordiant Off Road 2 — Cordiant Off Road 2 245/70R16 111Q</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E59" s="14" t="n">
-        <v>800</v>
+        <v>12066.66</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>560</v>
+        <v>10972.5</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>0.3</v>
+        <v>0.0906762931913222</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>оценка: 800 ₽ за «шт» — скорее упаковка ланцетов/скарификаторов-ручек (ТЗ нет); безопасные ланцеты 100 шт в опте ~500–700 ₽ — оценка, единица измерения требует проверки</t>
+          <t>Приморская шинная компания Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/avtoshina-245-70r16-111q-off-road-2-cordiant-g18320588579.html</t>
         </is>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>3. Перчатки смотровые/процедурные нитриловые, неопудренные, нестерильные</t>
+          <t>265/65R17 зимняя (Toyota LC Prado / Hilux / Pajero Sport) — Cordiant Snow Cross 2 SUV 265/65R17 116T (шип)</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>8000</v>
+        <v>4</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Пара (2 шт.)</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E60" s="14" t="n">
-        <v>10.34</v>
+        <v>16166.66</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>7</v>
+        <v>11941.5</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>0.3230174081237911</v>
+        <v>0.2613502108660664</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>Webpack: нитрил смотр. неопудр. 100 шт (50 пар) 400 ₽, опт от 69 уп. 350 ₽ → 7,0 ₽/пара https://webpack.ru/sredstva-individyalnoiy-zashitu/perchatki/perchatki-nitrilovye/ ; Trial Market ~390 ₽/100 шт</t>
+          <t>Шинсервис Владивосток: https://vladivostok.shinservice.ru/catalog/cordiant/winter/snow_cross2suv/265-65-R17/116T/?idx=864297</t>
         </is>
       </c>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>4. Шприц общего назначения</t>
+          <t>225/75R16C зимняя шип. КАМА Alga LT (УАЗ Профи/«буханка»); альт. 215/70R16 шип. (Viatti Bosco Nordico / Cordiant Snow Cr</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>4000</v>
+        <v>26</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E61" s="14" t="n">
-        <v>5.5</v>
+        <v>10466.66</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>3.8</v>
+        <v>9806.379999999999</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>0.3090909090909091</v>
+        <v>0.06308411661408708</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>НВ-Лаб: шприц 5 мл 3-комп. опт 3 ₽, розн. 4 ₽ https://www.nv-lab.ru/catalog_info.php?ID=6920 ; российский (Медполимер/СФМ) — оценка 3,8 ₽; объём шприца в карточке не указан (по цене 5,5 ₽ — 2–5 мл)</t>
+          <t>Автодонор Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/avtoshina-ship-kama-alga-lt-nk-534-225-75r16c-121-120r-nzhkm-1251004-g18384807651.html</t>
         </is>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>5. Игла для забора крови, стандартная</t>
+          <t>185/75R16C всесезон/лето — Forward Professional 301 185/75R16C</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E62" s="14" t="n">
-        <v>19.33</v>
+        <v>6766.66</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>4.22</v>
+        <v>4702.5</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>0.7816864976720124</v>
+        <v>0.3050485764025384</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>Sunmed: игла двусторонняя 21G «ЕЛАМЕД» (РФ) 8516 — 4,22 ₽ опт, цена на 14.04.2026 https://www.sunmed.ru/product/igla-dvustoronnyaya-dlya-vakuumnoy-sistemy-zabora-krovi-elamed-8516/</t>
+          <t>Приморская шинная компания Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/avtoshina-185-75r16c-tl-professional-301-forward-50091228.html</t>
         </is>
       </c>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>6. Бинт эластичный, нелатексный, нестерильный, одноразового использования</t>
+          <t>185/75R16C зимняя шип. КАМА Alga LT — КАМА Alga LT НК-534 185/75R16C 104/102R (шип)</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E63" s="14" t="n">
-        <v>315.67</v>
+        <v>7766.66</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>265</v>
+        <v>7087</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>0.1605157284505971</v>
+        <v>0.08750994636046894</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Комета-мед: бинт эласт. компрессионный 10 см×5 м Медитек — 295 ₽ https://kometa-med.com/product/bint-elastichnyj-kompressionnyj-meditek-sr-10-sm-h-5-m/ −10% торг ≈ 265 ₽; размер в карточке не указан</t>
+          <t>Автодонор Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/avtoshina-ship-kama-alga-lt-nk-534-185-75r16c-104-102r-nzhkm-1251003-g18384807650.html</t>
         </is>
       </c>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>7. Шприц общего назначения</t>
+          <t>225/75R16C (ГАЗель Next / Соболь 4x4) лето/всесезон КАМА Trace НК-135 — КАМА Trace НК-135 225/75R16C 121/120R</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Штука</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E64" s="14" t="n">
-        <v>12.34</v>
+        <v>9433.33</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>7.1</v>
+        <v>8711.5</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>0.4246353322528363</v>
+        <v>0.07651910831063902</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>оптовый прайс: шприц 3-комп. 20 мл — 7,90 ₽ (поиск по шприцевым оптовикам), другой магазин 5,10 ₽/шт (уп.100) → 7,1 ₽ после торга; объём в карточке не указан (10–20 мл)</t>
+          <t>ГРУЗШИНА (UNITYRE) Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/225-75r16lt-kama-nizhnekamskij-shinnyj-zavod-trace-nk-135-121-120r-rossija-letnie-legkovye-shiny-itvl8-g18106582521.html</t>
         </is>
       </c>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>0312100011426000102</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>8. Ватные шарики</t>
+          <t>185/75R16C зимняя нешип. (Viatti Vettore Brina) — или та же Alga LT, что п.7 — Viatti Vettore Brina V-525 185/75R16C 104</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Упаковка</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E65" s="14" t="n">
-        <v>296.34</v>
+        <v>7766.66</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>180</v>
+        <v>7087</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>0.3925895930350273</v>
+        <v>0.08750994636046894</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>оценка: «упаковка» без фасовки (ТЗ нет); шарики ватные нестерильные 100–200 шт/уп рос. пр-ва (Емельянъ Савостинъ, Амелия) — оценка 60% НМЦ</t>
+          <t>Shinapoint-Владивосток Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/viatti-vettore-brina-v-525-185-75r16c-104-102r-nzhkm-3250018-g18399043052.html</t>
         </is>
       </c>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>Портландцемент без минеральных добавок (ЦЕМ I 42,5Н / ПЦ500-Д0), мешки</t>
+          <t>14.00-20 ОИ-25 (Урал-4320/375); альт. 1300×530-533 ВИ-3 12PR — Алтайшина ОИ-25 14.00-20 (370-508) 14НС</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E66" s="14" t="n">
-        <v>14400</v>
+        <v>41333.33</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>11580</v>
+        <v>37002.5</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>0.1958333333333333</v>
+        <v>0.1047781536111415</v>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>579 ₽/50 кг (Цемрос ЦЕМ I 42,5Н, Сатурн Екатеринбург) = 11 580 ₽/т; Лемана ПРО 545 ₽/мешок: https://ekb.saturn.net/product/tsement-tsem-i-425n-m-500-d0-50-kg2/ ; https://ekaterinburg.lemanapro.ru/catalogue/cement/</t>
+          <t>Приморская шинная компания Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/avtoshina-14.00-20-370-508-tt-14ns-oi-25-altajshina-g17008525428.html</t>
         </is>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Щебень (фракция по ТЗ, предположительно 20-40)</t>
+          <t>1220×400-533 И-П184 (КАМАЗ-4310/43114); альт. 14.00-20 ОИ-25 — Forward Traction И-П184 1220×400-533 142G 10PR</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E67" s="14" t="n">
-        <v>792</v>
+        <v>37000</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>900</v>
+        <v>33440</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>-0.1363636363636365</v>
+        <v>0.09621621621621623</v>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>оценка: карьер от 550 ₽/м3 самовывоз (granit96), с доставкой 700–1350 ₽/м3, доставка ~95 ₽/км (ursdom), 15 м3 ≈ 21 т = 2 рейса: https://granit96.ru/katalog-produkczii/shheben-20-40.html ; https://dana96.ru/nerudnie/dostavka-shchebnya/ ; https://ursdo</t>
+          <t>ГРУЗШИНА (UNITYRE) Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/1220x400-533-forward-ip-184-142g-10pr-tt-rossija-gruzovye-shiny-rivl1-g18594431950.html</t>
         </is>
       </c>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>Песок (строительный, по ТЗ)</t>
+          <t>1300×530-533 ВИ-3 16PR (Урал-4320-31, КАМАЗ-43118 «вездеход»); альт. 16.00R20 КАМА PRO NU 404 — Омскшина ВИ-3 1300×530-5</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>654</v>
+        <v>70333.33</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>990</v>
+        <v>64581</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>-0.5137614678899083</v>
+        <v>0.08178668634060127</v>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>карьерный песок от 990 ₽/м3 с доставкой (от 470–500 ₽ без доставки): https://samosval-ekb.ru/pesok ; https://ural-grunt.ru/produktsiya/pesok</t>
+          <t>ГРУЗШИНА (UNITYRE) Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/1300x530-533-omskshina-vi-3-173b-16pr-tt-rossija-gruzovye-shiny-rivl13-g18594431942.html</t>
         </is>
       </c>
     </row>
     <row r="69" ht="60" customHeight="1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>0362100023526000014</t>
+          <t>0320100031626000249</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Труба стальная (диаметр/стенка в карточке не указаны; допущение — ВГП 25×3,2)</t>
+          <t>425/85R21 (КАМАЗ-4326/43118) КАМА-1260 / NorTec TR-1260 / TyRex — TyRex 425/85R21 20PR (2024 г.в.)</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>п.м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E69" s="14" t="n">
-        <v>300</v>
+        <v>55666.66</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>200</v>
+        <v>42750</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.2320358361719564</v>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>оценка при ВГП 25×3,2: 200 ₽/м (62 500 ₽/т, Стальавто), 114–180 ₽/м (МеталлНефтеПроект); при трубе 57×3,5 ≈ 4,6 кг/м × 62,5 тыс. ₽/т ≈ 290 ₽/м — маржи нет: https://stal-avto96.ru/truba-vgp/truba-vgp-25h32-du/ ; https://metallnp.ru/catalog/truba_vodog</t>
+          <t>АвтоСитиДВ Владивосток: https://baza.drom.ru/vladivostok/wheel/tire/tyrex-425-85r21-20pr-113592777.html</t>
         </is>
       </c>
     </row>
